--- a/serverFireStation/fire_station_project/report_templates/passenger_car.xlsx
+++ b/serverFireStation/fire_station_project/report_templates/passenger_car.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\server\serverFireStation\fire_station_project\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Дмитрий\Desktop\Diplom_Application\FFGSM\serverFireStation\fire_station_project\report_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158074C8-D65F-4D01-A344-7B27F8149CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B892E-9D91-4B80-87DA-663AA2EF38B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -246,26 +246,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -286,6 +275,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -316,39 +338,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -650,520 +639,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="31"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="28" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="21" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="27"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="29"/>
+      <c r="J4" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="11" t="s">
+      <c r="K4" s="26"/>
+      <c r="L4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="22" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
       <c r="H5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="13"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="22"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>4</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>6</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <v>7</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="3">
         <v>8</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="3">
         <v>9</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="5">
         <v>10</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="6">
         <v>11</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="7">
         <v>12</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="6">
         <v>13</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="6">
         <v>14</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="7">
         <v>15</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="G2:H2"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
@@ -1179,6 +841,13 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="68" orientation="landscape" r:id="rId1"/>
